--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -4611,7 +4611,7 @@
         <v>498173</v>
       </c>
       <c r="R42" t="n">
-        <v>6826082</v>
+        <v>6826081</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -10775,7 +10775,7 @@
         <v>498173</v>
       </c>
       <c r="R105" t="n">
-        <v>6826082</v>
+        <v>6826081</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -4611,7 +4611,7 @@
         <v>498173</v>
       </c>
       <c r="R42" t="n">
-        <v>6826081</v>
+        <v>6826082</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -10775,7 +10775,7 @@
         <v>498173</v>
       </c>
       <c r="R105" t="n">
-        <v>6826081</v>
+        <v>6826082</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>

--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AZ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565216</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567955</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563251</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564762</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566967</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568831</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568915</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568990</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569150</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563639</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565867</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567749</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569930</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569806</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562093</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562336</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562456</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3036,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562483</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563329</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563401</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3212,6 +3342,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564154</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3309,6 +3444,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564739</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3406,6 +3546,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565099</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3503,6 +3648,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565246</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3600,6 +3750,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565297</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3697,6 +3852,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565356</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3794,6 +3954,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565372</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3891,6 +4056,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565443</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3988,6 +4158,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565520</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4085,6 +4260,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565737</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4182,6 +4362,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565859</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4279,6 +4464,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4376,6 +4566,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566088</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4473,6 +4668,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566105</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4570,6 +4770,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566118</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4667,6 +4872,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566476</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4764,6 +4974,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566693</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4861,6 +5076,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566714</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4958,6 +5178,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566749</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5055,6 +5280,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567016</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5152,6 +5382,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567077</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5249,6 +5484,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567171</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5346,6 +5586,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567193</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5443,6 +5688,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567330</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5540,6 +5790,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567383</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5637,6 +5892,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567394</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5734,6 +5994,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567481</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5831,6 +6096,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567559</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5928,6 +6198,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567650</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6025,6 +6300,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567668</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6122,6 +6402,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567899</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6219,6 +6504,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567960</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6316,6 +6606,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567978</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6413,6 +6708,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568096</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6510,6 +6810,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568155</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6607,6 +6912,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568443</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6704,6 +7014,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568477</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6801,6 +7116,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568494</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6898,6 +7218,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568553</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6995,6 +7320,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568706</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7092,6 +7422,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568850</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7189,6 +7524,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568872</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7286,6 +7626,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569223</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7383,6 +7728,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569257</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7480,6 +7830,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569436</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7577,6 +7932,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569704</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7674,6 +8034,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569800</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7771,6 +8136,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134570003</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7868,6 +8238,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562169</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7965,6 +8340,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562184</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8062,6 +8442,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562676</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8159,6 +8544,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563613</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8256,6 +8646,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563685</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8353,6 +8748,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563699</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8450,6 +8850,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564223</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8547,6 +8952,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565635</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8644,6 +9054,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565655</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8741,6 +9156,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565881</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8838,6 +9258,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566065</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8935,6 +9360,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566207</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9032,6 +9462,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567490</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9129,6 +9564,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568112</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9226,6 +9666,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569575</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9323,6 +9768,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134570031</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9420,6 +9870,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563081</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9517,6 +9972,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563587</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9614,6 +10074,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562361</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9716,6 +10181,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562794</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9823,6 +10293,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567267</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9925,6 +10400,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568145</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10027,6 +10507,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569856</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10129,6 +10614,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564224</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10226,6 +10716,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565513</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10328,6 +10823,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562402</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10425,6 +10925,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569028</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10531,6 +11036,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566179</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10628,6 +11138,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566269</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10734,6 +11249,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566408</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10831,6 +11351,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566473</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10937,6 +11462,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566646</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11043,6 +11573,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566683</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11140,6 +11675,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566782</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11237,6 +11777,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566839</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11348,6 +11893,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566844</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11445,6 +11995,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567921</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11542,6 +12097,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568042</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11648,6 +12208,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569742</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11759,6 +12324,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567555</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11856,6 +12426,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567827</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11953,6 +12528,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562512</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12050,6 +12630,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134562645</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12147,6 +12732,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563028</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12244,6 +12834,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563498</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12341,6 +12936,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563668</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12438,6 +13038,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563679</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12535,6 +13140,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563693</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12632,6 +13242,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134563796</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12729,6 +13344,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564094</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12826,6 +13446,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564765</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12923,6 +13548,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565641</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13020,6 +13650,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565669</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13117,6 +13752,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566046</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13214,6 +13854,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566199</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13311,6 +13956,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566659</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13408,6 +14058,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567954</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13505,6 +14160,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568453</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13602,6 +14262,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568898</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13699,6 +14364,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569401</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13796,6 +14466,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569461</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13893,6 +14568,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569706</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13990,6 +14670,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569736</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14087,6 +14772,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569896</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14184,6 +14874,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569990</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14281,6 +14976,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564127</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14378,6 +15078,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564300</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14475,8 +15180,156 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27325-2026 artfynd.xlsx
+++ b/artfynd/A 27325-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ142"/>
+  <dimension ref="A1:AZ160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134563251</v>
+        <v>135905767</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498799</v>
+        <v>497853</v>
       </c>
       <c r="R8" t="n">
-        <v>6825663</v>
+        <v>6826265</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1357,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,24 +1387,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563251</t>
+          <t>https://artportalen.se/Sighting/135905767</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134564762</v>
+        <v>134563251</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498443</v>
+        <v>498799</v>
       </c>
       <c r="R9" t="n">
-        <v>6825767</v>
+        <v>6825663</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1490,13 +1500,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564762</t>
+          <t>https://artportalen.se/Sighting/134563251</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134565704</v>
+        <v>134564762</v>
       </c>
       <c r="B10" t="n">
         <v>79039</v>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498179</v>
+        <v>498443</v>
       </c>
       <c r="R10" t="n">
-        <v>6825861</v>
+        <v>6825767</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1592,13 +1602,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565704</t>
+          <t>https://artportalen.se/Sighting/134564762</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134566967</v>
+        <v>134565704</v>
       </c>
       <c r="B11" t="n">
         <v>79039</v>
@@ -1629,17 +1639,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498211</v>
+        <v>498179</v>
       </c>
       <c r="R11" t="n">
-        <v>6826135</v>
+        <v>6825861</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,24 +1693,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566967</t>
+          <t>https://artportalen.se/Sighting/134565704</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134568831</v>
+        <v>134566967</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1735,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498356</v>
+        <v>498211</v>
       </c>
       <c r="R12" t="n">
-        <v>6826240</v>
+        <v>6826135</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,24 +1795,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568831</t>
+          <t>https://artportalen.se/Sighting/134566967</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134568915</v>
+        <v>134568831</v>
       </c>
       <c r="B13" t="n">
         <v>79039</v>
@@ -1837,13 +1847,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498371</v>
+        <v>498356</v>
       </c>
       <c r="R13" t="n">
-        <v>6826151</v>
+        <v>6826240</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,24 +1897,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568915</t>
+          <t>https://artportalen.se/Sighting/134568831</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134568990</v>
+        <v>134568915</v>
       </c>
       <c r="B14" t="n">
         <v>79039</v>
@@ -1939,13 +1949,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498393</v>
+        <v>498371</v>
       </c>
       <c r="R14" t="n">
-        <v>6826077</v>
+        <v>6826151</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2000,13 +2010,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568990</t>
+          <t>https://artportalen.se/Sighting/134568915</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134569150</v>
+        <v>134568990</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498381</v>
+        <v>498393</v>
       </c>
       <c r="R15" t="n">
-        <v>6826007</v>
+        <v>6826077</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,16 +2112,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569150</t>
+          <t>https://artportalen.se/Sighting/134568990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134563639</v>
+        <v>134569150</v>
       </c>
       <c r="B16" t="n">
-        <v>90997</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,37 +2129,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498640</v>
+        <v>498381</v>
       </c>
       <c r="R16" t="n">
-        <v>6825626</v>
+        <v>6826007</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2193,27 +2203,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563639</t>
+          <t>https://artportalen.se/Sighting/134569150</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134565867</v>
+        <v>135891822</v>
       </c>
       <c r="B17" t="n">
-        <v>93271</v>
+        <v>81423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,46 +2231,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498162</v>
+        <v>497921</v>
       </c>
       <c r="R17" t="n">
-        <v>6825971</v>
+        <v>6826173</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2284,12 +2285,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2304,27 +2315,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565867</t>
+          <t>https://artportalen.se/Sighting/135891822</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134567749</v>
+        <v>134563639</v>
       </c>
       <c r="B18" t="n">
-        <v>93271</v>
+        <v>90997</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,37 +2343,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497962</v>
+        <v>498640</v>
       </c>
       <c r="R18" t="n">
-        <v>6826283</v>
+        <v>6825626</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2406,24 +2417,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567749</t>
+          <t>https://artportalen.se/Sighting/134563639</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134569930</v>
+        <v>134565867</v>
       </c>
       <c r="B19" t="n">
         <v>93271</v>
@@ -2463,14 +2474,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498653</v>
+        <v>498162</v>
       </c>
       <c r="R19" t="n">
-        <v>6825810</v>
+        <v>6825971</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2528,16 +2539,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569930</t>
+          <t>https://artportalen.se/Sighting/134565867</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134569806</v>
+        <v>134567749</v>
       </c>
       <c r="B20" t="n">
-        <v>91995</v>
+        <v>93271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,21 +2556,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498650</v>
+        <v>497962</v>
       </c>
       <c r="R20" t="n">
-        <v>6825777</v>
+        <v>6826283</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,65 +2630,74 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569806</t>
+          <t>https://artportalen.se/Sighting/134567749</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134562093</v>
+        <v>134569930</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hammerfestviken, Hammerfestviken, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498963</v>
+        <v>498653</v>
       </c>
       <c r="R21" t="n">
-        <v>6825750</v>
+        <v>6825810</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2721,65 +2741,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562093</t>
+          <t>https://artportalen.se/Sighting/134569930</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134562336</v>
+        <v>135905765</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>93347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498896</v>
+        <v>497847</v>
       </c>
       <c r="R22" t="n">
-        <v>6825707</v>
+        <v>6826262</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2803,12 +2823,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2823,65 +2853,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562336</t>
+          <t>https://artportalen.se/Sighting/135905765</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134562456</v>
+        <v>135905803</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>93347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498881</v>
+        <v>498119</v>
       </c>
       <c r="R23" t="n">
-        <v>6825680</v>
+        <v>6825836</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2905,12 +2935,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2925,65 +2965,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562456</t>
+          <t>https://artportalen.se/Sighting/135905803</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134562483</v>
+        <v>134569806</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>91995</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498870</v>
+        <v>498650</v>
       </c>
       <c r="R24" t="n">
-        <v>6825687</v>
+        <v>6825777</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3038,13 +3078,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562483</t>
+          <t>https://artportalen.se/Sighting/134569806</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134563329</v>
+        <v>134562093</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -3075,14 +3115,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Hammerfestviken, Hammerfestviken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498753</v>
+        <v>498963</v>
       </c>
       <c r="R25" t="n">
-        <v>6825650</v>
+        <v>6825750</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3140,13 +3180,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563329</t>
+          <t>https://artportalen.se/Sighting/134562093</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134563401</v>
+        <v>134562336</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3181,13 +3221,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498710</v>
+        <v>498896</v>
       </c>
       <c r="R26" t="n">
-        <v>6825641</v>
+        <v>6825707</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3242,13 +3282,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563401</t>
+          <t>https://artportalen.se/Sighting/134562336</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134564154</v>
+        <v>134562456</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3279,17 +3319,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498620</v>
+        <v>498881</v>
       </c>
       <c r="R27" t="n">
-        <v>6825657</v>
+        <v>6825680</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3333,24 +3373,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564154</t>
+          <t>https://artportalen.se/Sighting/134562456</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134564739</v>
+        <v>134562483</v>
       </c>
       <c r="B28" t="n">
         <v>79373</v>
@@ -3381,17 +3421,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498537</v>
+        <v>498870</v>
       </c>
       <c r="R28" t="n">
-        <v>6825729</v>
+        <v>6825687</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3435,24 +3475,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564739</t>
+          <t>https://artportalen.se/Sighting/134562483</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134565099</v>
+        <v>134563329</v>
       </c>
       <c r="B29" t="n">
         <v>79373</v>
@@ -3487,10 +3527,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498302</v>
+        <v>498753</v>
       </c>
       <c r="R29" t="n">
-        <v>6825879</v>
+        <v>6825650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,13 +3588,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565099</t>
+          <t>https://artportalen.se/Sighting/134563329</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134565246</v>
+        <v>134563401</v>
       </c>
       <c r="B30" t="n">
         <v>79373</v>
@@ -3589,13 +3629,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498257</v>
+        <v>498710</v>
       </c>
       <c r="R30" t="n">
-        <v>6825774</v>
+        <v>6825641</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3650,13 +3690,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565246</t>
+          <t>https://artportalen.se/Sighting/134563401</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134565297</v>
+        <v>134564154</v>
       </c>
       <c r="B31" t="n">
         <v>79373</v>
@@ -3691,10 +3731,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>498249</v>
+        <v>498620</v>
       </c>
       <c r="R31" t="n">
-        <v>6825777</v>
+        <v>6825657</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3752,13 +3792,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565297</t>
+          <t>https://artportalen.se/Sighting/134564154</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134565356</v>
+        <v>134564739</v>
       </c>
       <c r="B32" t="n">
         <v>79373</v>
@@ -3793,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>498239</v>
+        <v>498537</v>
       </c>
       <c r="R32" t="n">
-        <v>6825778</v>
+        <v>6825729</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3854,13 +3894,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565356</t>
+          <t>https://artportalen.se/Sighting/134564739</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134565372</v>
+        <v>134565099</v>
       </c>
       <c r="B33" t="n">
         <v>79373</v>
@@ -3891,17 +3931,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>498235</v>
+        <v>498302</v>
       </c>
       <c r="R33" t="n">
-        <v>6825748</v>
+        <v>6825879</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3945,24 +3985,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565372</t>
+          <t>https://artportalen.se/Sighting/134565099</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134565443</v>
+        <v>134565246</v>
       </c>
       <c r="B34" t="n">
         <v>79373</v>
@@ -3997,13 +4037,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>498199</v>
+        <v>498257</v>
       </c>
       <c r="R34" t="n">
-        <v>6825751</v>
+        <v>6825774</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4058,13 +4098,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565443</t>
+          <t>https://artportalen.se/Sighting/134565246</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134565520</v>
+        <v>134565297</v>
       </c>
       <c r="B35" t="n">
         <v>79373</v>
@@ -4095,17 +4135,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>498154</v>
+        <v>498249</v>
       </c>
       <c r="R35" t="n">
-        <v>6825804</v>
+        <v>6825777</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4149,24 +4189,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565520</t>
+          <t>https://artportalen.se/Sighting/134565297</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134565737</v>
+        <v>134565356</v>
       </c>
       <c r="B36" t="n">
         <v>79373</v>
@@ -4197,17 +4237,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>498157</v>
+        <v>498239</v>
       </c>
       <c r="R36" t="n">
-        <v>6825875</v>
+        <v>6825778</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4251,24 +4291,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565737</t>
+          <t>https://artportalen.se/Sighting/134565356</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134565859</v>
+        <v>134565372</v>
       </c>
       <c r="B37" t="n">
         <v>79373</v>
@@ -4303,10 +4343,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>498162</v>
+        <v>498235</v>
       </c>
       <c r="R37" t="n">
-        <v>6825971</v>
+        <v>6825748</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4364,13 +4404,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565859</t>
+          <t>https://artportalen.se/Sighting/134565372</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134566038</v>
+        <v>134565443</v>
       </c>
       <c r="B38" t="n">
         <v>79373</v>
@@ -4401,14 +4441,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>498218</v>
+        <v>498199</v>
       </c>
       <c r="R38" t="n">
-        <v>6825993</v>
+        <v>6825751</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,24 +4495,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566038</t>
+          <t>https://artportalen.se/Sighting/134565443</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134566088</v>
+        <v>134565520</v>
       </c>
       <c r="B39" t="n">
         <v>79373</v>
@@ -4507,10 +4547,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>498136</v>
+        <v>498154</v>
       </c>
       <c r="R39" t="n">
-        <v>6825992</v>
+        <v>6825804</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4568,13 +4608,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566088</t>
+          <t>https://artportalen.se/Sighting/134565520</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134566105</v>
+        <v>134565737</v>
       </c>
       <c r="B40" t="n">
         <v>79373</v>
@@ -4605,17 +4645,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>498222</v>
+        <v>498157</v>
       </c>
       <c r="R40" t="n">
-        <v>6826003</v>
+        <v>6825875</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4659,24 +4699,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566105</t>
+          <t>https://artportalen.se/Sighting/134565737</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134566118</v>
+        <v>134565859</v>
       </c>
       <c r="B41" t="n">
         <v>79373</v>
@@ -4711,10 +4751,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>498129</v>
+        <v>498162</v>
       </c>
       <c r="R41" t="n">
-        <v>6826004</v>
+        <v>6825971</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4772,13 +4812,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566118</t>
+          <t>https://artportalen.se/Sighting/134565859</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134566476</v>
+        <v>134566038</v>
       </c>
       <c r="B42" t="n">
         <v>79373</v>
@@ -4809,14 +4849,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>498173</v>
+        <v>498218</v>
       </c>
       <c r="R42" t="n">
-        <v>6826081</v>
+        <v>6825993</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,13 +4914,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566476</t>
+          <t>https://artportalen.se/Sighting/134566038</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134566693</v>
+        <v>134566088</v>
       </c>
       <c r="B43" t="n">
         <v>79373</v>
@@ -4915,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>498079</v>
+        <v>498136</v>
       </c>
       <c r="R43" t="n">
-        <v>6826108</v>
+        <v>6825992</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4976,13 +5016,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566693</t>
+          <t>https://artportalen.se/Sighting/134566088</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134566714</v>
+        <v>134566105</v>
       </c>
       <c r="B44" t="n">
         <v>79373</v>
@@ -5013,14 +5053,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>498187</v>
+        <v>498222</v>
       </c>
       <c r="R44" t="n">
-        <v>6826141</v>
+        <v>6826003</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5078,13 +5118,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566714</t>
+          <t>https://artportalen.se/Sighting/134566105</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134566749</v>
+        <v>134566118</v>
       </c>
       <c r="B45" t="n">
         <v>79373</v>
@@ -5119,13 +5159,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>498048</v>
+        <v>498129</v>
       </c>
       <c r="R45" t="n">
-        <v>6826116</v>
+        <v>6826004</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5180,13 +5220,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566749</t>
+          <t>https://artportalen.se/Sighting/134566118</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134567016</v>
+        <v>134566476</v>
       </c>
       <c r="B46" t="n">
         <v>79373</v>
@@ -5221,10 +5261,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>498211</v>
+        <v>498173</v>
       </c>
       <c r="R46" t="n">
-        <v>6826135</v>
+        <v>6826081</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5282,13 +5322,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567016</t>
+          <t>https://artportalen.se/Sighting/134566476</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134567077</v>
+        <v>134566693</v>
       </c>
       <c r="B47" t="n">
         <v>79373</v>
@@ -5319,17 +5359,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>498219</v>
+        <v>498079</v>
       </c>
       <c r="R47" t="n">
-        <v>6826173</v>
+        <v>6826108</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5373,24 +5413,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567077</t>
+          <t>https://artportalen.se/Sighting/134566693</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134567171</v>
+        <v>134566714</v>
       </c>
       <c r="B48" t="n">
         <v>79373</v>
@@ -5421,17 +5461,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497970</v>
+        <v>498187</v>
       </c>
       <c r="R48" t="n">
-        <v>6826175</v>
+        <v>6826141</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5475,24 +5515,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567171</t>
+          <t>https://artportalen.se/Sighting/134566714</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134567193</v>
+        <v>134566749</v>
       </c>
       <c r="B49" t="n">
         <v>79373</v>
@@ -5527,13 +5567,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497950</v>
+        <v>498048</v>
       </c>
       <c r="R49" t="n">
-        <v>6826165</v>
+        <v>6826116</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5588,13 +5628,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567193</t>
+          <t>https://artportalen.se/Sighting/134566749</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134567330</v>
+        <v>134567016</v>
       </c>
       <c r="B50" t="n">
         <v>79373</v>
@@ -5629,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>498214</v>
+        <v>498211</v>
       </c>
       <c r="R50" t="n">
-        <v>6826235</v>
+        <v>6826135</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5690,13 +5730,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567330</t>
+          <t>https://artportalen.se/Sighting/134567016</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134567383</v>
+        <v>134567077</v>
       </c>
       <c r="B51" t="n">
         <v>79373</v>
@@ -5727,17 +5767,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497936</v>
+        <v>498219</v>
       </c>
       <c r="R51" t="n">
-        <v>6826193</v>
+        <v>6826173</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5781,24 +5821,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567383</t>
+          <t>https://artportalen.se/Sighting/134567077</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134567394</v>
+        <v>134567171</v>
       </c>
       <c r="B52" t="n">
         <v>79373</v>
@@ -5829,17 +5869,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>498167</v>
+        <v>497970</v>
       </c>
       <c r="R52" t="n">
-        <v>6826215</v>
+        <v>6826175</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5883,24 +5923,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567394</t>
+          <t>https://artportalen.se/Sighting/134567171</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134567481</v>
+        <v>134567193</v>
       </c>
       <c r="B53" t="n">
         <v>79373</v>
@@ -5935,13 +5975,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497932</v>
+        <v>497950</v>
       </c>
       <c r="R53" t="n">
-        <v>6826210</v>
+        <v>6826165</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5996,13 +6036,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567481</t>
+          <t>https://artportalen.se/Sighting/134567193</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134567559</v>
+        <v>134567330</v>
       </c>
       <c r="B54" t="n">
         <v>79373</v>
@@ -6037,10 +6077,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>498096</v>
+        <v>498214</v>
       </c>
       <c r="R54" t="n">
-        <v>6826227</v>
+        <v>6826235</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,13 +6138,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567559</t>
+          <t>https://artportalen.se/Sighting/134567330</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134567650</v>
+        <v>134567383</v>
       </c>
       <c r="B55" t="n">
         <v>79373</v>
@@ -6135,17 +6175,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497966</v>
+        <v>497936</v>
       </c>
       <c r="R55" t="n">
-        <v>6826267</v>
+        <v>6826193</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6189,24 +6229,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567650</t>
+          <t>https://artportalen.se/Sighting/134567383</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134567668</v>
+        <v>134567394</v>
       </c>
       <c r="B56" t="n">
         <v>79373</v>
@@ -6237,17 +6277,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497948</v>
+        <v>498167</v>
       </c>
       <c r="R56" t="n">
-        <v>6826252</v>
+        <v>6826215</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6291,24 +6331,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567668</t>
+          <t>https://artportalen.se/Sighting/134567394</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134567899</v>
+        <v>134567481</v>
       </c>
       <c r="B57" t="n">
         <v>79373</v>
@@ -6339,17 +6379,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>498062</v>
+        <v>497932</v>
       </c>
       <c r="R57" t="n">
-        <v>6826301</v>
+        <v>6826210</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6393,24 +6433,24 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567899</t>
+          <t>https://artportalen.se/Sighting/134567481</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134567960</v>
+        <v>134567559</v>
       </c>
       <c r="B58" t="n">
         <v>79373</v>
@@ -6445,10 +6485,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>498089</v>
+        <v>498096</v>
       </c>
       <c r="R58" t="n">
-        <v>6826296</v>
+        <v>6826227</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6506,13 +6546,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567960</t>
+          <t>https://artportalen.se/Sighting/134567559</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134567978</v>
+        <v>134567650</v>
       </c>
       <c r="B59" t="n">
         <v>79373</v>
@@ -6547,10 +6587,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>498132</v>
+        <v>497966</v>
       </c>
       <c r="R59" t="n">
-        <v>6826277</v>
+        <v>6826267</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6608,13 +6648,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567978</t>
+          <t>https://artportalen.se/Sighting/134567650</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134568096</v>
+        <v>134567668</v>
       </c>
       <c r="B60" t="n">
         <v>79373</v>
@@ -6645,17 +6685,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>498194</v>
+        <v>497948</v>
       </c>
       <c r="R60" t="n">
-        <v>6826215</v>
+        <v>6826252</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6699,24 +6739,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568096</t>
+          <t>https://artportalen.se/Sighting/134567668</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134568155</v>
+        <v>134567899</v>
       </c>
       <c r="B61" t="n">
         <v>79373</v>
@@ -6751,10 +6791,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>498267</v>
+        <v>498062</v>
       </c>
       <c r="R61" t="n">
-        <v>6826206</v>
+        <v>6826301</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6812,13 +6852,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568155</t>
+          <t>https://artportalen.se/Sighting/134567899</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134568443</v>
+        <v>134567960</v>
       </c>
       <c r="B62" t="n">
         <v>79373</v>
@@ -6853,10 +6893,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>498344</v>
+        <v>498089</v>
       </c>
       <c r="R62" t="n">
-        <v>6826121</v>
+        <v>6826296</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6914,13 +6954,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568443</t>
+          <t>https://artportalen.se/Sighting/134567960</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134568477</v>
+        <v>134567978</v>
       </c>
       <c r="B63" t="n">
         <v>79373</v>
@@ -6955,10 +6995,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>498363</v>
+        <v>498132</v>
       </c>
       <c r="R63" t="n">
-        <v>6826140</v>
+        <v>6826277</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7016,13 +7056,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568477</t>
+          <t>https://artportalen.se/Sighting/134567978</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134568494</v>
+        <v>134568096</v>
       </c>
       <c r="B64" t="n">
         <v>79373</v>
@@ -7057,13 +7097,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>498330</v>
+        <v>498194</v>
       </c>
       <c r="R64" t="n">
-        <v>6826224</v>
+        <v>6826215</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7107,24 +7147,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568494</t>
+          <t>https://artportalen.se/Sighting/134568096</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134568553</v>
+        <v>134568155</v>
       </c>
       <c r="B65" t="n">
         <v>79373</v>
@@ -7159,13 +7199,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>498353</v>
+        <v>498267</v>
       </c>
       <c r="R65" t="n">
-        <v>6826244</v>
+        <v>6826206</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7220,13 +7260,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568553</t>
+          <t>https://artportalen.se/Sighting/134568155</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134568706</v>
+        <v>134568443</v>
       </c>
       <c r="B66" t="n">
         <v>79373</v>
@@ -7261,10 +7301,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>498339</v>
+        <v>498344</v>
       </c>
       <c r="R66" t="n">
-        <v>6826314</v>
+        <v>6826121</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,13 +7362,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568706</t>
+          <t>https://artportalen.se/Sighting/134568443</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134568850</v>
+        <v>134568477</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7363,13 +7403,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>498361</v>
+        <v>498363</v>
       </c>
       <c r="R67" t="n">
-        <v>6826236</v>
+        <v>6826140</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7413,24 +7453,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568850</t>
+          <t>https://artportalen.se/Sighting/134568477</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134568872</v>
+        <v>134568494</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -7465,13 +7505,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>498357</v>
+        <v>498330</v>
       </c>
       <c r="R68" t="n">
-        <v>6826187</v>
+        <v>6826224</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7515,24 +7555,24 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568872</t>
+          <t>https://artportalen.se/Sighting/134568494</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134569223</v>
+        <v>134568553</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -7567,13 +7607,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>498441</v>
+        <v>498353</v>
       </c>
       <c r="R69" t="n">
-        <v>6825961</v>
+        <v>6826244</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7628,13 +7668,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569223</t>
+          <t>https://artportalen.se/Sighting/134568553</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134569257</v>
+        <v>134568706</v>
       </c>
       <c r="B70" t="n">
         <v>79373</v>
@@ -7669,13 +7709,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>498519</v>
+        <v>498339</v>
       </c>
       <c r="R70" t="n">
-        <v>6825921</v>
+        <v>6826314</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7719,24 +7759,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569257</t>
+          <t>https://artportalen.se/Sighting/134568706</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134569436</v>
+        <v>134568850</v>
       </c>
       <c r="B71" t="n">
         <v>79373</v>
@@ -7771,13 +7811,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>498544</v>
+        <v>498361</v>
       </c>
       <c r="R71" t="n">
-        <v>6825861</v>
+        <v>6826236</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7832,13 +7872,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569436</t>
+          <t>https://artportalen.se/Sighting/134568850</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134569704</v>
+        <v>134568872</v>
       </c>
       <c r="B72" t="n">
         <v>79373</v>
@@ -7869,14 +7909,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>498629</v>
+        <v>498357</v>
       </c>
       <c r="R72" t="n">
-        <v>6825840</v>
+        <v>6826187</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7934,13 +7974,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569704</t>
+          <t>https://artportalen.se/Sighting/134568872</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134569800</v>
+        <v>134569223</v>
       </c>
       <c r="B73" t="n">
         <v>79373</v>
@@ -7971,17 +8011,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>498616</v>
+        <v>498441</v>
       </c>
       <c r="R73" t="n">
-        <v>6825799</v>
+        <v>6825961</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8036,13 +8076,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569800</t>
+          <t>https://artportalen.se/Sighting/134569223</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134570003</v>
+        <v>134569257</v>
       </c>
       <c r="B74" t="n">
         <v>79373</v>
@@ -8073,17 +8113,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>498749</v>
+        <v>498519</v>
       </c>
       <c r="R74" t="n">
-        <v>6825750</v>
+        <v>6825921</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8127,65 +8167,65 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134570003</t>
+          <t>https://artportalen.se/Sighting/134569257</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134562169</v>
+        <v>134569436</v>
       </c>
       <c r="B75" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hammerfestviken, Hammerfestviken, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>498963</v>
+        <v>498544</v>
       </c>
       <c r="R75" t="n">
-        <v>6825726</v>
+        <v>6825861</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8229,65 +8269,65 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562169</t>
+          <t>https://artportalen.se/Sighting/134569436</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134562184</v>
+        <v>134569704</v>
       </c>
       <c r="B76" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hammerfestviken, Hammerfestviken, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>498966</v>
+        <v>498629</v>
       </c>
       <c r="R76" t="n">
-        <v>6825724</v>
+        <v>6825840</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8342,54 +8382,54 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562184</t>
+          <t>https://artportalen.se/Sighting/134569704</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134562676</v>
+        <v>134569800</v>
       </c>
       <c r="B77" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>498878</v>
+        <v>498616</v>
       </c>
       <c r="R77" t="n">
-        <v>6825631</v>
+        <v>6825799</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8433,65 +8473,65 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562676</t>
+          <t>https://artportalen.se/Sighting/134569800</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134563613</v>
+        <v>134570003</v>
       </c>
       <c r="B78" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>498649</v>
+        <v>498749</v>
       </c>
       <c r="R78" t="n">
-        <v>6825622</v>
+        <v>6825750</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8535,65 +8575,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563613</t>
+          <t>https://artportalen.se/Sighting/134570003</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134563685</v>
+        <v>135891828</v>
       </c>
       <c r="B79" t="n">
-        <v>79130</v>
+        <v>79441</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>498626</v>
+        <v>497820</v>
       </c>
       <c r="R79" t="n">
-        <v>6825664</v>
+        <v>6826282</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8617,12 +8657,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8637,65 +8687,65 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563685</t>
+          <t>https://artportalen.se/Sighting/135891828</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134563699</v>
+        <v>135905768</v>
       </c>
       <c r="B80" t="n">
-        <v>79130</v>
+        <v>79441</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>498619</v>
+        <v>497879</v>
       </c>
       <c r="R80" t="n">
-        <v>6825619</v>
+        <v>6826254</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8719,12 +8769,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8739,65 +8799,65 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563699</t>
+          <t>https://artportalen.se/Sighting/135905768</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134564223</v>
+        <v>135905799</v>
       </c>
       <c r="B81" t="n">
-        <v>79130</v>
+        <v>79441</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>498601</v>
+        <v>498112</v>
       </c>
       <c r="R81" t="n">
-        <v>6825662</v>
+        <v>6825882</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8821,12 +8881,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8841,65 +8911,65 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564223</t>
+          <t>https://artportalen.se/Sighting/135905799</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134565635</v>
+        <v>135905801</v>
       </c>
       <c r="B82" t="n">
-        <v>79130</v>
+        <v>79441</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>498160</v>
+        <v>498123</v>
       </c>
       <c r="R82" t="n">
-        <v>6825837</v>
+        <v>6825845</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8923,12 +8993,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8943,24 +9023,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565635</t>
+          <t>https://artportalen.se/Sighting/135905801</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134565655</v>
+        <v>134562169</v>
       </c>
       <c r="B83" t="n">
         <v>79130</v>
@@ -8991,17 +9071,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Hammerfestviken, Hammerfestviken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>498166</v>
+        <v>498963</v>
       </c>
       <c r="R83" t="n">
-        <v>6825861</v>
+        <v>6825726</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9045,24 +9125,24 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565655</t>
+          <t>https://artportalen.se/Sighting/134562169</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134565881</v>
+        <v>134562184</v>
       </c>
       <c r="B84" t="n">
         <v>79130</v>
@@ -9093,17 +9173,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Hammerfestviken, Hammerfestviken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>498165</v>
+        <v>498966</v>
       </c>
       <c r="R84" t="n">
-        <v>6825980</v>
+        <v>6825724</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9147,24 +9227,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565881</t>
+          <t>https://artportalen.se/Sighting/134562184</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134566065</v>
+        <v>134562676</v>
       </c>
       <c r="B85" t="n">
         <v>79130</v>
@@ -9199,10 +9279,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>498139</v>
+        <v>498878</v>
       </c>
       <c r="R85" t="n">
-        <v>6825980</v>
+        <v>6825631</v>
       </c>
       <c r="S85" t="n">
         <v>20</v>
@@ -9260,13 +9340,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566065</t>
+          <t>https://artportalen.se/Sighting/134562676</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134566207</v>
+        <v>134563613</v>
       </c>
       <c r="B86" t="n">
         <v>79130</v>
@@ -9301,10 +9381,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>498138</v>
+        <v>498649</v>
       </c>
       <c r="R86" t="n">
-        <v>6826013</v>
+        <v>6825622</v>
       </c>
       <c r="S86" t="n">
         <v>20</v>
@@ -9362,13 +9442,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566207</t>
+          <t>https://artportalen.se/Sighting/134563613</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134567490</v>
+        <v>134563685</v>
       </c>
       <c r="B87" t="n">
         <v>79130</v>
@@ -9399,14 +9479,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>498164</v>
+        <v>498626</v>
       </c>
       <c r="R87" t="n">
-        <v>6826214</v>
+        <v>6825664</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9464,13 +9544,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567490</t>
+          <t>https://artportalen.se/Sighting/134563685</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134568112</v>
+        <v>134563699</v>
       </c>
       <c r="B88" t="n">
         <v>79130</v>
@@ -9505,13 +9585,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>498235</v>
+        <v>498619</v>
       </c>
       <c r="R88" t="n">
-        <v>6826134</v>
+        <v>6825619</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9566,13 +9646,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568112</t>
+          <t>https://artportalen.se/Sighting/134563699</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134569575</v>
+        <v>134564223</v>
       </c>
       <c r="B89" t="n">
         <v>79130</v>
@@ -9603,14 +9683,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>498573</v>
+        <v>498601</v>
       </c>
       <c r="R89" t="n">
-        <v>6825862</v>
+        <v>6825662</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -9668,13 +9748,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569575</t>
+          <t>https://artportalen.se/Sighting/134564223</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134570031</v>
+        <v>134565635</v>
       </c>
       <c r="B90" t="n">
         <v>79130</v>
@@ -9705,14 +9785,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>498677</v>
+        <v>498160</v>
       </c>
       <c r="R90" t="n">
-        <v>6825787</v>
+        <v>6825837</v>
       </c>
       <c r="S90" t="n">
         <v>20</v>
@@ -9770,16 +9850,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134570031</t>
+          <t>https://artportalen.se/Sighting/134565635</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134563081</v>
+        <v>134565655</v>
       </c>
       <c r="B91" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9787,21 +9867,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9811,13 +9891,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>498831</v>
+        <v>498166</v>
       </c>
       <c r="R91" t="n">
-        <v>6825647</v>
+        <v>6825861</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9872,16 +9952,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563081</t>
+          <t>https://artportalen.se/Sighting/134565655</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134563587</v>
+        <v>134565881</v>
       </c>
       <c r="B92" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9889,21 +9969,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9913,13 +9993,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>498655</v>
+        <v>498165</v>
       </c>
       <c r="R92" t="n">
-        <v>6825637</v>
+        <v>6825980</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9974,38 +10054,38 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563587</t>
+          <t>https://artportalen.se/Sighting/134565881</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134562361</v>
+        <v>134566065</v>
       </c>
       <c r="B93" t="n">
-        <v>80493</v>
+        <v>79130</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10015,10 +10095,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>498890</v>
+        <v>498139</v>
       </c>
       <c r="R93" t="n">
-        <v>6825709</v>
+        <v>6825980</v>
       </c>
       <c r="S93" t="n">
         <v>20</v>
@@ -10076,16 +10156,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562361</t>
+          <t>https://artportalen.se/Sighting/134566065</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134562794</v>
+        <v>134566207</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10093,21 +10173,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10117,10 +10197,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>498863</v>
+        <v>498138</v>
       </c>
       <c r="R94" t="n">
-        <v>6825638</v>
+        <v>6826013</v>
       </c>
       <c r="S94" t="n">
         <v>20</v>
@@ -10155,11 +10235,6 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack tall.</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10183,16 +10258,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562794</t>
+          <t>https://artportalen.se/Sighting/134566207</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134567267</v>
+        <v>134567490</v>
       </c>
       <c r="B95" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10200,39 +10275,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>498213</v>
+        <v>498164</v>
       </c>
       <c r="R95" t="n">
-        <v>6826232</v>
+        <v>6826214</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10267,11 +10337,6 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10295,16 +10360,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567267</t>
+          <t>https://artportalen.se/Sighting/134567490</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134568145</v>
+        <v>134568112</v>
       </c>
       <c r="B96" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10312,37 +10377,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>498255</v>
+        <v>498235</v>
       </c>
       <c r="R96" t="n">
-        <v>6826222</v>
+        <v>6826134</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10372,11 +10437,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10391,49 +10451,49 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568145</t>
+          <t>https://artportalen.se/Sighting/134568112</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134569856</v>
+        <v>134569575</v>
       </c>
       <c r="B97" t="n">
-        <v>57162</v>
+        <v>79130</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10443,10 +10503,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>498627</v>
+        <v>498573</v>
       </c>
       <c r="R97" t="n">
-        <v>6825828</v>
+        <v>6825862</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10481,11 +10541,6 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10509,16 +10564,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569856</t>
+          <t>https://artportalen.se/Sighting/134569575</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134564224</v>
+        <v>134570031</v>
       </c>
       <c r="B98" t="n">
-        <v>58136</v>
+        <v>79130</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10526,39 +10581,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>498537</v>
+        <v>498677</v>
       </c>
       <c r="R98" t="n">
-        <v>6825729</v>
+        <v>6825787</v>
       </c>
       <c r="S98" t="n">
         <v>20</v>
@@ -10605,27 +10655,27 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564224</t>
+          <t>https://artportalen.se/Sighting/134570031</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134565513</v>
+        <v>134563081</v>
       </c>
       <c r="B99" t="n">
-        <v>58136</v>
+        <v>79992</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10633,37 +10683,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>498156</v>
+        <v>498831</v>
       </c>
       <c r="R99" t="n">
-        <v>6825862</v>
+        <v>6825647</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10707,49 +10757,49 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565513</t>
+          <t>https://artportalen.se/Sighting/134563081</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134562402</v>
+        <v>134563587</v>
       </c>
       <c r="B100" t="n">
-        <v>8460</v>
+        <v>79992</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10759,13 +10809,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>498873</v>
+        <v>498655</v>
       </c>
       <c r="R100" t="n">
-        <v>6825702</v>
+        <v>6825637</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10795,11 +10845,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Måsvingar på stående torrtall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10825,54 +10870,54 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562402</t>
+          <t>https://artportalen.se/Sighting/134563587</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134569028</v>
+        <v>135891820</v>
       </c>
       <c r="B101" t="n">
-        <v>8460</v>
+        <v>80060</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>498393</v>
+        <v>497940</v>
       </c>
       <c r="R101" t="n">
-        <v>6826077</v>
+        <v>6826163</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10896,12 +10941,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10916,71 +10971,62 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569028</t>
+          <t>https://artportalen.se/Sighting/135891820</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134566179</v>
+        <v>135905761</v>
       </c>
       <c r="B102" t="n">
-        <v>99195</v>
+        <v>80060</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>498209</v>
+        <v>497876</v>
       </c>
       <c r="R102" t="n">
-        <v>6826065</v>
+        <v>6826205</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11007,12 +11053,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11027,65 +11083,65 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566179</t>
+          <t>https://artportalen.se/Sighting/135905761</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134566269</v>
+        <v>135905770</v>
       </c>
       <c r="B103" t="n">
-        <v>99195</v>
+        <v>80060</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>498184</v>
+        <v>497879</v>
       </c>
       <c r="R103" t="n">
-        <v>6826067</v>
+        <v>6826203</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11109,12 +11165,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11129,71 +11195,62 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566269</t>
+          <t>https://artportalen.se/Sighting/135905770</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134566408</v>
+        <v>134562361</v>
       </c>
       <c r="B104" t="n">
-        <v>99195</v>
+        <v>80493</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>498165</v>
+        <v>498890</v>
       </c>
       <c r="R104" t="n">
-        <v>6826032</v>
+        <v>6825709</v>
       </c>
       <c r="S104" t="n">
         <v>20</v>
@@ -11251,54 +11308,54 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566408</t>
+          <t>https://artportalen.se/Sighting/134562361</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134566473</v>
+        <v>134562794</v>
       </c>
       <c r="B105" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>498173</v>
+        <v>498863</v>
       </c>
       <c r="R105" t="n">
-        <v>6826081</v>
+        <v>6825638</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11328,6 +11385,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11342,59 +11404,55 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566473</t>
+          <t>https://artportalen.se/Sighting/134562794</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134566646</v>
+        <v>134567267</v>
       </c>
       <c r="B106" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11403,10 +11461,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>498175</v>
+        <v>498213</v>
       </c>
       <c r="R106" t="n">
-        <v>6826109</v>
+        <v>6826232</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11441,6 +11499,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11464,60 +11527,51 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566646</t>
+          <t>https://artportalen.se/Sighting/134567267</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134566683</v>
+        <v>134568145</v>
       </c>
       <c r="B107" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>498178</v>
+        <v>498255</v>
       </c>
       <c r="R107" t="n">
-        <v>6826131</v>
+        <v>6826222</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11552,6 +11606,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11575,38 +11634,38 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566683</t>
+          <t>https://artportalen.se/Sighting/134568145</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134566782</v>
+        <v>134569856</v>
       </c>
       <c r="B108" t="n">
-        <v>99195</v>
+        <v>57162</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11616,13 +11675,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>498208</v>
+        <v>498627</v>
       </c>
       <c r="R108" t="n">
-        <v>6826135</v>
+        <v>6825828</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11652,6 +11711,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11666,65 +11730,70 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566782</t>
+          <t>https://artportalen.se/Sighting/134569856</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134566839</v>
+        <v>134564224</v>
       </c>
       <c r="B109" t="n">
-        <v>99195</v>
+        <v>58136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>498213</v>
+        <v>498537</v>
       </c>
       <c r="R109" t="n">
-        <v>6826138</v>
+        <v>6825729</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11779,68 +11848,54 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566839</t>
+          <t>https://artportalen.se/Sighting/134564224</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134566844</v>
+        <v>134565513</v>
       </c>
       <c r="B110" t="n">
-        <v>99195</v>
+        <v>58136</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>498037</v>
+        <v>498156</v>
       </c>
       <c r="R110" t="n">
-        <v>6826127</v>
+        <v>6825862</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11884,65 +11939,65 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566844</t>
+          <t>https://artportalen.se/Sighting/134565513</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134567921</v>
+        <v>134562402</v>
       </c>
       <c r="B111" t="n">
-        <v>99195</v>
+        <v>8460</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>498089</v>
+        <v>498873</v>
       </c>
       <c r="R111" t="n">
-        <v>6826296</v>
+        <v>6825702</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11972,6 +12027,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Måsvingar på stående torrtall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11986,49 +12046,49 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567921</t>
+          <t>https://artportalen.se/Sighting/134562402</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134568042</v>
+        <v>134569028</v>
       </c>
       <c r="B112" t="n">
-        <v>99195</v>
+        <v>8460</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12038,10 +12098,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>498174</v>
+        <v>498393</v>
       </c>
       <c r="R112" t="n">
-        <v>6826241</v>
+        <v>6826077</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12099,63 +12159,54 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568042</t>
+          <t>https://artportalen.se/Sighting/134569028</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134569742</v>
+        <v>135905766</v>
       </c>
       <c r="B113" t="n">
-        <v>99195</v>
+        <v>8461</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>498601</v>
+        <v>497848</v>
       </c>
       <c r="R113" t="n">
-        <v>6825841</v>
+        <v>6826263</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12179,12 +12230,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12199,27 +12260,27 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569742</t>
+          <t>https://artportalen.se/Sighting/135905766</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134567555</v>
+        <v>135905771</v>
       </c>
       <c r="B114" t="n">
-        <v>106324</v>
+        <v>8461</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12227,51 +12288,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497934</v>
+        <v>497882</v>
       </c>
       <c r="R114" t="n">
-        <v>6826210</v>
+        <v>6826192</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12295,12 +12342,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12315,27 +12372,27 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Karla Alfaro Gripe, Erik Christiansson, Malte Lindberg, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567555</t>
+          <t>https://artportalen.se/Sighting/135905771</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134567827</v>
+        <v>135905798</v>
       </c>
       <c r="B115" t="n">
-        <v>106324</v>
+        <v>8461</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12343,37 +12400,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497964</v>
+        <v>498112</v>
       </c>
       <c r="R115" t="n">
-        <v>6826280</v>
+        <v>6825882</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12397,12 +12454,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12417,65 +12484,65 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567827</t>
+          <t>https://artportalen.se/Sighting/135905798</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134562512</v>
+        <v>135905800</v>
       </c>
       <c r="B116" t="n">
-        <v>79131</v>
+        <v>8461</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>498863</v>
+        <v>498132</v>
       </c>
       <c r="R116" t="n">
-        <v>6825687</v>
+        <v>6825856</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12499,12 +12566,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12519,65 +12596,65 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562512</t>
+          <t>https://artportalen.se/Sighting/135905800</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134562645</v>
+        <v>135905804</v>
       </c>
       <c r="B117" t="n">
-        <v>79131</v>
+        <v>8461</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>498874</v>
+        <v>498120</v>
       </c>
       <c r="R117" t="n">
-        <v>6825629</v>
+        <v>6825829</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12601,12 +12678,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12621,65 +12708,74 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134562645</t>
+          <t>https://artportalen.se/Sighting/135905804</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134563028</v>
+        <v>134566179</v>
       </c>
       <c r="B118" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>498855</v>
+        <v>498209</v>
       </c>
       <c r="R118" t="n">
-        <v>6825636</v>
+        <v>6826065</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12723,65 +12819,65 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563028</t>
+          <t>https://artportalen.se/Sighting/134566179</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134563498</v>
+        <v>134566269</v>
       </c>
       <c r="B119" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>498694</v>
+        <v>498184</v>
       </c>
       <c r="R119" t="n">
-        <v>6825636</v>
+        <v>6826067</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12836,54 +12932,63 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563498</t>
+          <t>https://artportalen.se/Sighting/134566269</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134563668</v>
+        <v>134566408</v>
       </c>
       <c r="B120" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>498649</v>
+        <v>498165</v>
       </c>
       <c r="R120" t="n">
-        <v>6825646</v>
+        <v>6826032</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12927,62 +13032,62 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563668</t>
+          <t>https://artportalen.se/Sighting/134566408</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134563679</v>
+        <v>134566473</v>
       </c>
       <c r="B121" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>498626</v>
+        <v>498173</v>
       </c>
       <c r="R121" t="n">
-        <v>6825664</v>
+        <v>6826081</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13040,54 +13145,63 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563679</t>
+          <t>https://artportalen.se/Sighting/134566473</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134563693</v>
+        <v>134566646</v>
       </c>
       <c r="B122" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>498619</v>
+        <v>498175</v>
       </c>
       <c r="R122" t="n">
-        <v>6825619</v>
+        <v>6826109</v>
       </c>
       <c r="S122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13131,65 +13245,74 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563693</t>
+          <t>https://artportalen.se/Sighting/134566646</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134563796</v>
+        <v>134566683</v>
       </c>
       <c r="B123" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>498600</v>
+        <v>498178</v>
       </c>
       <c r="R123" t="n">
-        <v>6825635</v>
+        <v>6826131</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13233,65 +13356,65 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134563796</t>
+          <t>https://artportalen.se/Sighting/134566683</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134564094</v>
+        <v>134566782</v>
       </c>
       <c r="B124" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>498614</v>
+        <v>498208</v>
       </c>
       <c r="R124" t="n">
-        <v>6825652</v>
+        <v>6826135</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13335,62 +13458,62 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564094</t>
+          <t>https://artportalen.se/Sighting/134566782</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134564765</v>
+        <v>134566839</v>
       </c>
       <c r="B125" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>498537</v>
+        <v>498213</v>
       </c>
       <c r="R125" t="n">
-        <v>6825729</v>
+        <v>6826138</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13448,51 +13571,65 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564765</t>
+          <t>https://artportalen.se/Sighting/134566839</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134565641</v>
+        <v>134566844</v>
       </c>
       <c r="B126" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>498147</v>
+        <v>498037</v>
       </c>
       <c r="R126" t="n">
-        <v>6825857</v>
+        <v>6826127</v>
       </c>
       <c r="S126" t="n">
         <v>20</v>
@@ -13550,54 +13687,54 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565641</t>
+          <t>https://artportalen.se/Sighting/134566844</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134565669</v>
+        <v>134567921</v>
       </c>
       <c r="B127" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>498155</v>
+        <v>498089</v>
       </c>
       <c r="R127" t="n">
-        <v>6825864</v>
+        <v>6826296</v>
       </c>
       <c r="S127" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13641,62 +13778,62 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134565669</t>
+          <t>https://artportalen.se/Sighting/134567921</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134566046</v>
+        <v>134568042</v>
       </c>
       <c r="B128" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>498222</v>
+        <v>498174</v>
       </c>
       <c r="R128" t="n">
-        <v>6826003</v>
+        <v>6826241</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13754,51 +13891,60 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566046</t>
+          <t>https://artportalen.se/Sighting/134568042</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134566199</v>
+        <v>134569742</v>
       </c>
       <c r="B129" t="n">
-        <v>79131</v>
+        <v>99195</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>498138</v>
+        <v>498601</v>
       </c>
       <c r="R129" t="n">
-        <v>6826013</v>
+        <v>6825841</v>
       </c>
       <c r="S129" t="n">
         <v>20</v>
@@ -13856,51 +14002,65 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566199</t>
+          <t>https://artportalen.se/Sighting/134569742</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134566659</v>
+        <v>134567555</v>
       </c>
       <c r="B130" t="n">
-        <v>79131</v>
+        <v>106324</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>498090</v>
+        <v>497934</v>
       </c>
       <c r="R130" t="n">
-        <v>6826135</v>
+        <v>6826210</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -13958,38 +14118,38 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134566659</t>
+          <t>https://artportalen.se/Sighting/134567555</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134567954</v>
+        <v>134567827</v>
       </c>
       <c r="B131" t="n">
-        <v>79131</v>
+        <v>106324</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13999,10 +14159,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>498089</v>
+        <v>497964</v>
       </c>
       <c r="R131" t="n">
-        <v>6826296</v>
+        <v>6826280</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14060,54 +14220,54 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134567954</t>
+          <t>https://artportalen.se/Sighting/134567827</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134568453</v>
+        <v>135891827</v>
       </c>
       <c r="B132" t="n">
-        <v>79131</v>
+        <v>106413</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Storhamrasjön, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>498311</v>
+        <v>497821</v>
       </c>
       <c r="R132" t="n">
-        <v>6826218</v>
+        <v>6826281</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14131,12 +14291,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14151,24 +14321,24 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Nora Toftgård Shahnavaz, Tilde Carlinger, Alexander Ahl, Alma Strandanger</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568453</t>
+          <t>https://artportalen.se/Sighting/135891827</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134568898</v>
+        <v>134562512</v>
       </c>
       <c r="B133" t="n">
         <v>79131</v>
@@ -14199,17 +14369,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>498357</v>
+        <v>498863</v>
       </c>
       <c r="R133" t="n">
-        <v>6826187</v>
+        <v>6825687</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14253,24 +14423,24 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134568898</t>
+          <t>https://artportalen.se/Sighting/134562512</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134569401</v>
+        <v>134562645</v>
       </c>
       <c r="B134" t="n">
         <v>79131</v>
@@ -14301,17 +14471,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>498509</v>
+        <v>498874</v>
       </c>
       <c r="R134" t="n">
-        <v>6825901</v>
+        <v>6825629</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14355,24 +14525,24 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569401</t>
+          <t>https://artportalen.se/Sighting/134562645</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134569461</v>
+        <v>134563028</v>
       </c>
       <c r="B135" t="n">
         <v>79131</v>
@@ -14403,14 +14573,14 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>498548</v>
+        <v>498855</v>
       </c>
       <c r="R135" t="n">
-        <v>6825853</v>
+        <v>6825636</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -14468,13 +14638,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569461</t>
+          <t>https://artportalen.se/Sighting/134563028</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134569706</v>
+        <v>134563498</v>
       </c>
       <c r="B136" t="n">
         <v>79131</v>
@@ -14505,17 +14675,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>498595</v>
+        <v>498694</v>
       </c>
       <c r="R136" t="n">
-        <v>6825844</v>
+        <v>6825636</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14559,24 +14729,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569706</t>
+          <t>https://artportalen.se/Sighting/134563498</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134569736</v>
+        <v>134563668</v>
       </c>
       <c r="B137" t="n">
         <v>79131</v>
@@ -14611,10 +14781,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>498624</v>
+        <v>498649</v>
       </c>
       <c r="R137" t="n">
-        <v>6825838</v>
+        <v>6825646</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14672,13 +14842,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569736</t>
+          <t>https://artportalen.se/Sighting/134563668</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134569896</v>
+        <v>134563679</v>
       </c>
       <c r="B138" t="n">
         <v>79131</v>
@@ -14713,13 +14883,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>498621</v>
+        <v>498626</v>
       </c>
       <c r="R138" t="n">
-        <v>6825756</v>
+        <v>6825664</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14774,13 +14944,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569896</t>
+          <t>https://artportalen.se/Sighting/134563679</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>134569990</v>
+        <v>134563693</v>
       </c>
       <c r="B139" t="n">
         <v>79131</v>
@@ -14811,17 +14981,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>498734</v>
+        <v>498619</v>
       </c>
       <c r="R139" t="n">
-        <v>6825749</v>
+        <v>6825619</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14865,27 +15035,27 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134569990</t>
+          <t>https://artportalen.se/Sighting/134563693</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>134564127</v>
+        <v>134563796</v>
       </c>
       <c r="B140" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14893,21 +15063,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14917,10 +15087,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>498613</v>
+        <v>498600</v>
       </c>
       <c r="R140" t="n">
-        <v>6825647</v>
+        <v>6825635</v>
       </c>
       <c r="S140" t="n">
         <v>20</v>
@@ -14978,16 +15148,16 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564127</t>
+          <t>https://artportalen.se/Sighting/134563796</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134564300</v>
+        <v>134564094</v>
       </c>
       <c r="B141" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14995,21 +15165,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15019,13 +15189,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>498580</v>
+        <v>498614</v>
       </c>
       <c r="R141" t="n">
-        <v>6825684</v>
+        <v>6825652</v>
       </c>
       <c r="S141" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15080,16 +15250,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134564300</t>
+          <t>https://artportalen.se/Sighting/134564094</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134564813</v>
+        <v>134564765</v>
       </c>
       <c r="B142" t="n">
-        <v>79963</v>
+        <v>79131</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15097,21 +15267,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15181,6 +15351,1852 @@
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564765</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>134565641</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>498147</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6825857</v>
+      </c>
+      <c r="S143" t="n">
+        <v>20</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565641</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>134565669</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>498155</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6825864</v>
+      </c>
+      <c r="S144" t="n">
+        <v>20</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134565669</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>134566046</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>498222</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6826003</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566046</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>134566199</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>498138</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6826013</v>
+      </c>
+      <c r="S146" t="n">
+        <v>20</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566199</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>134566659</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>498090</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6826135</v>
+      </c>
+      <c r="S147" t="n">
+        <v>20</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134566659</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>134567954</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>498089</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6826296</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134567954</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>134568453</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>498311</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6826218</v>
+      </c>
+      <c r="S149" t="n">
+        <v>20</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568453</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>134568898</v>
+      </c>
+      <c r="B150" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>498357</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6826187</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134568898</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>134569401</v>
+      </c>
+      <c r="B151" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>498509</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6825901</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569401</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>134569461</v>
+      </c>
+      <c r="B152" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>498548</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6825853</v>
+      </c>
+      <c r="S152" t="n">
+        <v>20</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569461</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>134569706</v>
+      </c>
+      <c r="B153" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Lagarenlattsmyrorna, Lagarenlattsmyrorna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>498595</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6825844</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569706</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>134569736</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>498624</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6825838</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569736</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>134569896</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>498621</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6825756</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569896</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>134569990</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>498734</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6825749</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134569990</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>135905792</v>
+      </c>
+      <c r="B157" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Storhamrasjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>498069</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6825957</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Alma Strandanger , Alexander Ahl, Malte Lindberg, Erik Christiansson, Karla Alfaro Gripe, Tilde Carlinger</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135905792</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>134564127</v>
+      </c>
+      <c r="B158" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>498613</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6825647</v>
+      </c>
+      <c r="S158" t="n">
+        <v>20</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564127</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>134564300</v>
+      </c>
+      <c r="B159" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Lagarenlatt, Lagarenlatt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>498580</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6825684</v>
+      </c>
+      <c r="S159" t="n">
+        <v>20</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134564300</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>134564813</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>498537</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6825729</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134564813</t>
         </is>
@@ -15329,6 +17345,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
